--- a/data/ingredientsToAdd.xlsx
+++ b/data/ingredientsToAdd.xlsx
@@ -5,15 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tarladalal-playwright-hybrid-js\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tarladalal-playwright-Hackathon\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8090BC7B-C258-453B-B83C-EA602FF1E008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2656EC-F9E7-485B-9AE6-2C53B7E98C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Ingredients" sheetId="1" r:id="rId1"/>
+    <sheet name="LCH ADD" sheetId="1" r:id="rId1"/>
+    <sheet name="LCH ELIMINATE" sheetId="2" r:id="rId2"/>
+    <sheet name="LFV ADD" sheetId="3" r:id="rId3"/>
+    <sheet name="LFV ELIMINATE" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="217">
   <si>
     <t>Ingredient</t>
   </si>
@@ -52,6 +55,630 @@
   </si>
   <si>
     <t>strawberry</t>
+  </si>
+  <si>
+    <t>Ginger</t>
+  </si>
+  <si>
+    <t>Butter</t>
+  </si>
+  <si>
+    <t>ghee</t>
+  </si>
+  <si>
+    <t>hard cheese</t>
+  </si>
+  <si>
+    <t>paneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cottage cheese </t>
+  </si>
+  <si>
+    <t xml:space="preserve">sour cream </t>
+  </si>
+  <si>
+    <t>greek yogurt</t>
+  </si>
+  <si>
+    <t>hung curd</t>
+  </si>
+  <si>
+    <t>almond</t>
+  </si>
+  <si>
+    <t>pistachio</t>
+  </si>
+  <si>
+    <t>brazil nut</t>
+  </si>
+  <si>
+    <t>walnut</t>
+  </si>
+  <si>
+    <t>pine nut</t>
+  </si>
+  <si>
+    <t>hazelnut</t>
+  </si>
+  <si>
+    <t>macadamia nut</t>
+  </si>
+  <si>
+    <t>pecan</t>
+  </si>
+  <si>
+    <t>hemp seed</t>
+  </si>
+  <si>
+    <t>sunflower seed</t>
+  </si>
+  <si>
+    <t>sesame seed</t>
+  </si>
+  <si>
+    <t>chia seed</t>
+  </si>
+  <si>
+    <t>flax seed</t>
+  </si>
+  <si>
+    <t>Blueberry</t>
+  </si>
+  <si>
+    <t>blackberry</t>
+  </si>
+  <si>
+    <t>Ham</t>
+  </si>
+  <si>
+    <t>sausage</t>
+  </si>
+  <si>
+    <t>tinned fish</t>
+  </si>
+  <si>
+    <t>tuna</t>
+  </si>
+  <si>
+    <t>sardines</t>
+  </si>
+  <si>
+    <t>yams</t>
+  </si>
+  <si>
+    <t>beets</t>
+  </si>
+  <si>
+    <t>parsnip</t>
+  </si>
+  <si>
+    <t>turnip</t>
+  </si>
+  <si>
+    <t>rutabagas</t>
+  </si>
+  <si>
+    <t>carrot</t>
+  </si>
+  <si>
+    <t>yuca</t>
+  </si>
+  <si>
+    <t>kohlrabi</t>
+  </si>
+  <si>
+    <t>celery root</t>
+  </si>
+  <si>
+    <t>horseradish</t>
+  </si>
+  <si>
+    <t>daikon</t>
+  </si>
+  <si>
+    <t>jicama</t>
+  </si>
+  <si>
+    <t>radish</t>
+  </si>
+  <si>
+    <t>pumpkin</t>
+  </si>
+  <si>
+    <t>squash</t>
+  </si>
+  <si>
+    <t>Whole fat milk</t>
+  </si>
+  <si>
+    <t>low fat milk</t>
+  </si>
+  <si>
+    <t>fat free milk</t>
+  </si>
+  <si>
+    <t>Evaporated milk</t>
+  </si>
+  <si>
+    <t>condensed milk</t>
+  </si>
+  <si>
+    <t>curd</t>
+  </si>
+  <si>
+    <t>buttermilk</t>
+  </si>
+  <si>
+    <t>ice cream</t>
+  </si>
+  <si>
+    <t>flavored milk</t>
+  </si>
+  <si>
+    <t>sweetened yogurt</t>
+  </si>
+  <si>
+    <t>soft cheese</t>
+  </si>
+  <si>
+    <t>grain</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>oat</t>
+  </si>
+  <si>
+    <t>barely</t>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>millet</t>
+  </si>
+  <si>
+    <t>jowar</t>
+  </si>
+  <si>
+    <t>bajra</t>
+  </si>
+  <si>
+    <t>corn</t>
+  </si>
+  <si>
+    <t>dal</t>
+  </si>
+  <si>
+    <t>lentil</t>
+  </si>
+  <si>
+    <t>banana</t>
+  </si>
+  <si>
+    <t>mango</t>
+  </si>
+  <si>
+    <t>papaya</t>
+  </si>
+  <si>
+    <t>plantain</t>
+  </si>
+  <si>
+    <t>apple</t>
+  </si>
+  <si>
+    <t>orange</t>
+  </si>
+  <si>
+    <t>pineapple</t>
+  </si>
+  <si>
+    <t>pear</t>
+  </si>
+  <si>
+    <t>tangerine</t>
+  </si>
+  <si>
+    <t>all melon varieties</t>
+  </si>
+  <si>
+    <t>peach</t>
+  </si>
+  <si>
+    <t>plum</t>
+  </si>
+  <si>
+    <t>nectarine</t>
+  </si>
+  <si>
+    <t>Avocado</t>
+  </si>
+  <si>
+    <t>olive oil</t>
+  </si>
+  <si>
+    <t>coconut oil</t>
+  </si>
+  <si>
+    <t>soybean oil</t>
+  </si>
+  <si>
+    <t>corn oil</t>
+  </si>
+  <si>
+    <t>safflower oil</t>
+  </si>
+  <si>
+    <t>sunflower oil</t>
+  </si>
+  <si>
+    <t>rapeseed oil</t>
+  </si>
+  <si>
+    <t>peanut oil</t>
+  </si>
+  <si>
+    <t>cottonseed oil</t>
+  </si>
+  <si>
+    <t>canola oil</t>
+  </si>
+  <si>
+    <t>mustard oil</t>
+  </si>
+  <si>
+    <t>sugar</t>
+  </si>
+  <si>
+    <t>jaggery</t>
+  </si>
+  <si>
+    <t>glucose</t>
+  </si>
+  <si>
+    <t>fructose</t>
+  </si>
+  <si>
+    <t>corn syrup</t>
+  </si>
+  <si>
+    <t>cane sugar</t>
+  </si>
+  <si>
+    <t>aspartame</t>
+  </si>
+  <si>
+    <t>cane solids</t>
+  </si>
+  <si>
+    <t>maltose</t>
+  </si>
+  <si>
+    <t>dextrose</t>
+  </si>
+  <si>
+    <t>sorbitol</t>
+  </si>
+  <si>
+    <t>mannitol</t>
+  </si>
+  <si>
+    <t>xylitol</t>
+  </si>
+  <si>
+    <t>maltodextrin</t>
+  </si>
+  <si>
+    <t>molasses</t>
+  </si>
+  <si>
+    <t>brown rice syrup</t>
+  </si>
+  <si>
+    <t>splenda</t>
+  </si>
+  <si>
+    <t>nutra sweet</t>
+  </si>
+  <si>
+    <t>stevia</t>
+  </si>
+  <si>
+    <t>barley malt</t>
+  </si>
+  <si>
+    <t>potato</t>
+  </si>
+  <si>
+    <t>pea</t>
+  </si>
+  <si>
+    <t>Lettuce</t>
+  </si>
+  <si>
+    <t>kale</t>
+  </si>
+  <si>
+    <t>chard</t>
+  </si>
+  <si>
+    <t>arugula</t>
+  </si>
+  <si>
+    <t>spinach</t>
+  </si>
+  <si>
+    <t>cabbage</t>
+  </si>
+  <si>
+    <t>sweet potatoes</t>
+  </si>
+  <si>
+    <t>purple potatoes</t>
+  </si>
+  <si>
+    <t>karela</t>
+  </si>
+  <si>
+    <t>bittergourd</t>
+  </si>
+  <si>
+    <t>beet</t>
+  </si>
+  <si>
+    <t>cucumber</t>
+  </si>
+  <si>
+    <t>red onion</t>
+  </si>
+  <si>
+    <t>white onion</t>
+  </si>
+  <si>
+    <t>broccoli</t>
+  </si>
+  <si>
+    <t>cauliflower</t>
+  </si>
+  <si>
+    <t>celery</t>
+  </si>
+  <si>
+    <t>artichoke</t>
+  </si>
+  <si>
+    <t>bell pepper</t>
+  </si>
+  <si>
+    <t>mushroom</t>
+  </si>
+  <si>
+    <t>tomato</t>
+  </si>
+  <si>
+    <t>sweet and hot pepper</t>
+  </si>
+  <si>
+    <t>all berry varieties</t>
+  </si>
+  <si>
+    <t>Amaranth</t>
+  </si>
+  <si>
+    <t>Rajgira</t>
+  </si>
+  <si>
+    <t>Ramdana Barnyard</t>
+  </si>
+  <si>
+    <t>Sanwa</t>
+  </si>
+  <si>
+    <t>Samvat ke chawal buckwheat</t>
+  </si>
+  <si>
+    <t>kuttu finger millet</t>
+  </si>
+  <si>
+    <t>Ragi</t>
+  </si>
+  <si>
+    <t>Nachni foxtail millet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kangni </t>
+  </si>
+  <si>
+    <t>kakum kodu</t>
+  </si>
+  <si>
+    <t>kodon</t>
+  </si>
+  <si>
+    <t>little millet</t>
+  </si>
+  <si>
+    <t>moraiyo</t>
+  </si>
+  <si>
+    <t>kutki</t>
+  </si>
+  <si>
+    <t>shavan</t>
+  </si>
+  <si>
+    <t>sama pearl millet</t>
+  </si>
+  <si>
+    <t>broom corn millet</t>
+  </si>
+  <si>
+    <t>chena sorghum</t>
+  </si>
+  <si>
+    <t>Lentil</t>
+  </si>
+  <si>
+    <t>Pulse</t>
+  </si>
+  <si>
+    <t>Moong dhal</t>
+  </si>
+  <si>
+    <t>masoor dhal</t>
+  </si>
+  <si>
+    <t>toor dhal</t>
+  </si>
+  <si>
+    <t>urd dhal</t>
+  </si>
+  <si>
+    <t>lobia</t>
+  </si>
+  <si>
+    <t>rajma</t>
+  </si>
+  <si>
+    <t>matar</t>
+  </si>
+  <si>
+    <t>all forms of chana</t>
+  </si>
+  <si>
+    <t>cashew</t>
+  </si>
+  <si>
+    <t>peanut</t>
+  </si>
+  <si>
+    <t>sun flower seed</t>
+  </si>
+  <si>
+    <t>pork</t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
+    <t>Poultry</t>
+  </si>
+  <si>
+    <t>Sausage</t>
+  </si>
+  <si>
+    <t>ham</t>
+  </si>
+  <si>
+    <t>salami</t>
+  </si>
+  <si>
+    <t>bacon</t>
+  </si>
+  <si>
+    <t>milk</t>
+  </si>
+  <si>
+    <t>cheese</t>
+  </si>
+  <si>
+    <t>yogurt</t>
+  </si>
+  <si>
+    <t>butter</t>
+  </si>
+  <si>
+    <t>Ice cream</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>cereals</t>
+  </si>
+  <si>
+    <t>tinned vegetable</t>
+  </si>
+  <si>
+    <t>bread</t>
+  </si>
+  <si>
+    <t>maida</t>
+  </si>
+  <si>
+    <t>atta</t>
+  </si>
+  <si>
+    <t>sooji</t>
+  </si>
+  <si>
+    <t>poha</t>
+  </si>
+  <si>
+    <t>cornflake</t>
+  </si>
+  <si>
+    <t>cornflour</t>
+  </si>
+  <si>
+    <t>pasta</t>
+  </si>
+  <si>
+    <t>White rice</t>
+  </si>
+  <si>
+    <t>pastry</t>
+  </si>
+  <si>
+    <t>cakes</t>
+  </si>
+  <si>
+    <t>biscuit</t>
+  </si>
+  <si>
+    <t>soy</t>
+  </si>
+  <si>
+    <t>soy milk</t>
+  </si>
+  <si>
+    <t>white miso paste</t>
+  </si>
+  <si>
+    <t>soy sauce</t>
+  </si>
+  <si>
+    <t>soy curls</t>
+  </si>
+  <si>
+    <t>edamame</t>
+  </si>
+  <si>
+    <t>soy yogurt</t>
+  </si>
+  <si>
+    <t>soy nut</t>
+  </si>
+  <si>
+    <t>tofu</t>
+  </si>
+  <si>
+    <t>pies</t>
+  </si>
+  <si>
+    <t>Chip</t>
+  </si>
+  <si>
+    <t>cracker</t>
+  </si>
+  <si>
+    <t>potatoe</t>
+  </si>
+  <si>
+    <t>cane solid</t>
   </si>
 </sst>
 </file>
@@ -130,18 +757,220 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A0E57EF1-8566-40F6-B687-365DE12D2BD5}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -155,9 +984,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="IngredientsTable" displayName="IngredientsTable" ref="A1:A9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="IngredientsTable" displayName="IngredientsTable" ref="A1:A33" dataDxfId="7">
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Ingredient"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Ingredient" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{525D083F-7B50-4ABB-A645-7A77829EB0C3}" name="IngredientsTable3" displayName="IngredientsTable3" ref="A1:A91" dataDxfId="5">
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{C25C1EF3-07C5-46B6-BE53-65A8FF6C48CB}" name="Ingredient" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{76B16ED9-18B1-4BAB-B501-35EAFF3FFD1B}" name="IngredientsTable4" displayName="IngredientsTable4" ref="A1:A89" dataDxfId="3">
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{9A28992E-A320-402A-803A-1C534DE45C7A}" name="Ingredient" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{ADEFC78C-9F68-4AE1-9D1A-E8788EBEEEAD}" name="IngredientsTable5" displayName="IngredientsTable5" ref="A1:A75" dataDxfId="1">
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{85AB27F6-E840-404C-A16B-A5274594B857}" name="Ingredient" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -312,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
@@ -360,7 +1216,1450 @@
     </row>
     <row r="9" spans="1:1" ht="14.4">
       <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="14.4">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="14.4">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="14.4">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="14.4">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="14.4">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="14.4">
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="14.4">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="14.4">
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="14.4">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="14.4">
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="14.4">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="14.4">
+      <c r="A21" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="14.4">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="14.4">
+      <c r="A23" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="14.4">
+      <c r="A24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="14.4">
+      <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="14.4">
+      <c r="A26" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="14.4">
+      <c r="A27" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="14.4">
+      <c r="A28" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="14.4">
+      <c r="A29" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="14.4">
+      <c r="A30" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="14.4">
+      <c r="A31" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="14.4">
+      <c r="A32" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="14.4">
+      <c r="A33" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B0ADBF-4607-4F41-B0A1-DE2C86D437E5}">
+  <dimension ref="A1:A91"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="14.4">
+      <c r="A2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="14.4">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="14.4">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="14.4">
+      <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="14.4">
+      <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="14.4">
+      <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="14.4">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="14.4">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="14.4">
+      <c r="A10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="14.4">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="14.4">
+      <c r="A12" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="14.4">
+      <c r="A13" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="14.4">
+      <c r="A14" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="14.4">
+      <c r="A15" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="14.4">
+      <c r="A16" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="14.4">
+      <c r="A17" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="14.4">
+      <c r="A18" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="14.4">
+      <c r="A19" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="14.4">
+      <c r="A20" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="14.4">
+      <c r="A21" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="14.4">
+      <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="14.4">
+      <c r="A23" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="14.4">
+      <c r="A24" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="14.4">
+      <c r="A25" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="14.4">
+      <c r="A26" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="14.4">
+      <c r="A27" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="14.4">
+      <c r="A28" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="14.4">
+      <c r="A29" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="14.4">
+      <c r="A30" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="14.4">
+      <c r="A31" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="14.4">
+      <c r="A32" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="14.4">
+      <c r="A33" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="14.4">
+      <c r="A34" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="14.4">
+      <c r="A35" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="14.4">
+      <c r="A36" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="14.4">
+      <c r="A37" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="14.4">
+      <c r="A38" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="14.4">
+      <c r="A39" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="14.4">
+      <c r="A40" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="14.4">
+      <c r="A41" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="14.4">
+      <c r="A42" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="14.4">
+      <c r="A43" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="14.4">
+      <c r="A44" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="14.4">
+      <c r="A45" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="14.4">
+      <c r="A46" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="14.4">
+      <c r="A47" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="14.4">
+      <c r="A48" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="14.4">
+      <c r="A49" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="14.4">
+      <c r="A50" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="14.4">
+      <c r="A51" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="14.4">
+      <c r="A52" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="14.4">
+      <c r="A53" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="14.4">
+      <c r="A54" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="14.4">
+      <c r="A55" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="14.4">
+      <c r="A56" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="14.4">
+      <c r="A57" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="14.4">
+      <c r="A58" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="14.4">
+      <c r="A59" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="14.4">
+      <c r="A60" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="14.4">
+      <c r="A61" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="14.4">
+      <c r="A62" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="14.4">
+      <c r="A63" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="14.4">
+      <c r="A64" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="14.4">
+      <c r="A65" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="14.4">
+      <c r="A66" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="14.4">
+      <c r="A67" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="14.4">
+      <c r="A68" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="14.4">
+      <c r="A69" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="14.4">
+      <c r="A70" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="14.4">
+      <c r="A71" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="14.4">
+      <c r="A72" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="14.4">
+      <c r="A73" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="14.4">
+      <c r="A74" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="14.4">
+      <c r="A75" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="14.4">
+      <c r="A76" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="14.4">
+      <c r="A77" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="14.4">
+      <c r="A78" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="14.4">
+      <c r="A79" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="14.4">
+      <c r="A80" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="14.4">
+      <c r="A81" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="14.4">
+      <c r="A82" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="14.4">
+      <c r="A83" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="14.4">
+      <c r="A84" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="14.4">
+      <c r="A85" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="14.4">
+      <c r="A86" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="14.4">
+      <c r="A87" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="14.4">
+      <c r="A88" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="14.4">
+      <c r="A89" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="14.4">
+      <c r="A90" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="14.4">
+      <c r="A91" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F54E49A6-3225-44AB-86A2-72DE17F140E2}">
+  <dimension ref="A1:A89"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="14.4">
+      <c r="A2" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="14.4">
+      <c r="A3" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="14.4">
+      <c r="A4" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="14.4">
+      <c r="A5" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="14.4">
+      <c r="A6" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="14.4">
+      <c r="A7" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="14.4">
+      <c r="A8" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="14.4">
+      <c r="A9" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="14.4">
+      <c r="A10" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="14.4">
+      <c r="A11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="14.4">
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="14.4">
+      <c r="A13" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="14.4">
+      <c r="A14" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="14.4">
+      <c r="A15" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="14.4">
+      <c r="A16" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="14.4">
+      <c r="A17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="14.4">
+      <c r="A18" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="14.4">
+      <c r="A19" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="14.4">
+      <c r="A20" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="14.4">
+      <c r="A21" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="14.4">
+      <c r="A22" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="14.4">
+      <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="14.4">
+      <c r="A24" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="14.4">
+      <c r="A25" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="14.4">
+      <c r="A26" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="14.4">
+      <c r="A27" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="14.4">
+      <c r="A28" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="14.4">
+      <c r="A29" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="14.4">
+      <c r="A30" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="14.4">
+      <c r="A31" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="14.4">
+      <c r="A32" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="14.4">
+      <c r="A33" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="14.4">
+      <c r="A34" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="14.4">
+      <c r="A35" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="14.4">
+      <c r="A36" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="14.4">
+      <c r="A37" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="14.4">
+      <c r="A38" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="14.4">
+      <c r="A39" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="14.4">
+      <c r="A40" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="14.4">
+      <c r="A41" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="14.4">
+      <c r="A42" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="14.4">
+      <c r="A43" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="14.4">
+      <c r="A44" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="14.4">
+      <c r="A45" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="14.4">
+      <c r="A46" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="14.4">
+      <c r="A47" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="14.4">
+      <c r="A48" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="14.4">
+      <c r="A49" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="14.4">
+      <c r="A50" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="14.4">
+      <c r="A51" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="14.4">
+      <c r="A52" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="14.4">
+      <c r="A53" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="14.4">
+      <c r="A54" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="14.4">
+      <c r="A55" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="14.4">
+      <c r="A56" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="14.4">
+      <c r="A57" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="14.4">
+      <c r="A58" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="14.4">
+      <c r="A59" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="14.4">
+      <c r="A60" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="14.4">
+      <c r="A61" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="14.4">
+      <c r="A62" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="14.4">
+      <c r="A63" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="14.4">
+      <c r="A64" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="14.4">
+      <c r="A65" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="14.4">
+      <c r="A66" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="14.4">
+      <c r="A67" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="14.4">
+      <c r="A68" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="14.4">
+      <c r="A69" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="14.4">
+      <c r="A70" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="14.4">
+      <c r="A71" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="14.4">
+      <c r="A72" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="14.4">
+      <c r="A73" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="14.4">
+      <c r="A74" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="14.4">
+      <c r="A75" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="14.4">
+      <c r="A76" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="14.4">
+      <c r="A77" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="14.4">
+      <c r="A78" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="14.4">
+      <c r="A79" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="14.4">
+      <c r="A80" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="14.4">
+      <c r="A81" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="14.4">
+      <c r="A82" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="14.4">
+      <c r="A83" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="14.4">
+      <c r="A84" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="14.4">
+      <c r="A85" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="14.4">
+      <c r="A86" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="14.4">
+      <c r="A87" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="14.4">
+      <c r="A88" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="14.4">
+      <c r="A89" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D9D164-FAD0-4E84-9819-3BE4D2494F62}">
+  <dimension ref="A1:A75"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="14.4">
+      <c r="A2" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="14.4">
+      <c r="A3" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="14.4">
+      <c r="A4" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="14.4">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="14.4">
+      <c r="A6" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="14.4">
+      <c r="A7" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="14.4">
+      <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="14.4">
+      <c r="A9" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="14.4">
+      <c r="A10" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="14.4">
+      <c r="A11" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="14.4">
+      <c r="A12" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="14.4">
+      <c r="A13" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="14.4">
+      <c r="A14" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="14.4">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="14.4">
+      <c r="A16" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="14.4">
+      <c r="A17" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="14.4">
+      <c r="A18" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="14.4">
+      <c r="A19" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="14.4">
+      <c r="A20" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="14.4">
+      <c r="A21" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="14.4">
+      <c r="A22" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="14.4">
+      <c r="A23" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="14.4">
+      <c r="A24" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="14.4">
+      <c r="A25" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="14.4">
+      <c r="A26" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="14.4">
+      <c r="A27" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="14.4">
+      <c r="A28" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="14.4">
+      <c r="A29" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="14.4">
+      <c r="A30" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="14.4">
+      <c r="A31" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="14.4">
+      <c r="A32" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="14.4">
+      <c r="A33" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="14.4">
+      <c r="A34" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="14.4">
+      <c r="A35" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="14.4">
+      <c r="A36" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="14.4">
+      <c r="A37" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="14.4">
+      <c r="A38" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="14.4">
+      <c r="A39" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="14.4">
+      <c r="A40" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="14.4">
+      <c r="A41" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="14.4">
+      <c r="A42" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="14.4">
+      <c r="A43" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="14.4">
+      <c r="A44" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="14.4">
+      <c r="A45" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="14.4">
+      <c r="A46" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="14.4">
+      <c r="A47" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="14.4">
+      <c r="A48" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="14.4">
+      <c r="A49" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="14.4">
+      <c r="A50" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="14.4">
+      <c r="A51" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="14.4">
+      <c r="A52" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="14.4">
+      <c r="A53" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="14.4">
+      <c r="A54" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="14.4">
+      <c r="A55" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="14.4">
+      <c r="A56" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="14.4">
+      <c r="A57" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="14.4">
+      <c r="A58" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="14.4">
+      <c r="A59" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="14.4">
+      <c r="A60" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="14.4">
+      <c r="A61" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="14.4">
+      <c r="A62" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="14.4">
+      <c r="A63" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="14.4">
+      <c r="A64" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="14.4">
+      <c r="A65" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="14.4">
+      <c r="A66" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="14.4">
+      <c r="A67" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="14.4">
+      <c r="A68" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="14.4">
+      <c r="A69" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="14.4">
+      <c r="A70" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="14.4">
+      <c r="A71" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="14.4">
+      <c r="A72" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="14.4">
+      <c r="A73" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="14.4">
+      <c r="A74" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="14.4">
+      <c r="A75" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/ingredientsToAdd.xlsx
+++ b/data/ingredientsToAdd.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tarladalal-playwright-Hackathon\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2656EC-F9E7-485B-9AE6-2C53B7E98C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90B906A-AD08-4CEB-BAC0-0E270A38F15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="LCH ADD" sheetId="1" r:id="rId1"/>
-    <sheet name="LCH ELIMINATE" sheetId="2" r:id="rId2"/>
-    <sheet name="LFV ADD" sheetId="3" r:id="rId3"/>
-    <sheet name="LFV ELIMINATE" sheetId="4" r:id="rId4"/>
+    <sheet name="LCH_ADD" sheetId="1" r:id="rId1"/>
+    <sheet name="LCH_ELIMINATE" sheetId="2" r:id="rId2"/>
+    <sheet name="LFV_ADD" sheetId="3" r:id="rId3"/>
+    <sheet name="LFV_ELIMINATE" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -1823,7 +1823,7 @@
   <dimension ref="A1:A89"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
